--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="182">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-pregnancy-status.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-pregnancy-status.header.langue</t>
+    <t>fr-lm-pregnancy-status.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-pregnancy-status.observationDate[x]</t>
@@ -479,32 +479,20 @@
     <t>Resultat de l'observation</t>
   </si>
   <si>
-    <t>fr-lm-pregnancy-status.result.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
     <t>fr-lm-pregnancy-status.result.value[x]</t>
   </si>
   <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Statut de grossesse de la patiente</t>
-  </si>
-  <si>
-    <t>Statut de grossesse de la patiente (enceinte, pas enceinte, etc.).</t>
-  </si>
-  <si>
-    <t>jdv-statut-grossesse-cisis (1.2.250.1.213.1.1.5.671)</t>
+    <t>string
+QuantityRangeRatioCodeableConcept</t>
+  </si>
+  <si>
+    <t>Valeur du resultat</t>
+  </si>
+  <si>
+    <t>Statut de grossesse de la patiente (enceinte, pas enceinte, etc.)</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-statut-grossesse-cisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>fr-lm-pregnancy-status.result.uncertainty</t>
@@ -897,7 +885,7 @@
   <cols>
     <col min="1" max="1" width="62.95703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="62.95703125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -919,7 +907,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="51.4765625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="55.21875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3147,11 +3135,9 @@
         <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>73</v>
       </c>
@@ -3172,13 +3158,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3208,26 +3194,28 @@
         <v>73</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="AC23" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
       <c r="AD23" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3244,10 +3232,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3273,10 +3261,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3327,7 +3315,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3344,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3370,13 +3358,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3427,7 +3415,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3444,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3470,13 +3458,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3527,7 +3515,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3544,10 +3532,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3573,10 +3561,10 @@
         <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3627,7 +3615,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3644,10 +3632,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3670,13 +3658,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3727,7 +3715,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3744,10 +3732,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3773,10 +3761,10 @@
         <v>80</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3827,7 +3815,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3844,10 +3832,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3870,13 +3858,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3927,7 +3915,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3944,10 +3932,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3970,13 +3958,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4006,10 +3994,10 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4027,7 +4015,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4044,10 +4032,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4070,13 +4058,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4106,10 +4094,10 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>73</v>
@@ -4127,7 +4115,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="180">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,7 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -2594,31 +2588,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2632,10 +2626,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2661,10 +2655,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2715,7 +2709,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2732,10 +2726,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2761,10 +2755,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2815,7 +2809,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2832,10 +2826,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2858,13 +2852,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2915,7 +2909,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2932,10 +2926,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2961,10 +2955,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3015,7 +3009,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3032,10 +3026,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3061,10 +3055,10 @@
         <v>80</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3115,7 +3109,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3132,10 +3126,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3158,13 +3152,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3194,10 +3188,10 @@
         <v>73</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>73</v>
@@ -3215,7 +3209,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3232,10 +3226,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3261,10 +3255,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3315,7 +3309,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3332,10 +3326,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3358,13 +3352,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3415,7 +3409,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3432,10 +3426,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3458,13 +3452,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3515,7 +3509,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3532,10 +3526,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3561,10 +3555,10 @@
         <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3615,7 +3609,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3632,10 +3626,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3658,13 +3652,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3715,7 +3709,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3732,10 +3726,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3761,10 +3755,10 @@
         <v>80</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3815,7 +3809,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3832,10 +3826,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3858,13 +3852,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3915,7 +3909,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3932,10 +3926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3958,13 +3952,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -3994,10 +3988,10 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>73</v>
@@ -4015,7 +4009,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4032,10 +4026,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4058,13 +4052,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4094,10 +4088,10 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>73</v>
@@ -4115,7 +4109,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-pregnancy-status.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
